--- a/survey_templates/042_eco_program_outcome_report_form--survey_templates.xlsx
+++ b/survey_templates/042_eco_program_outcome_report_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>program_area</t>
+          <t>program_title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Program Area</t>
+          <t>Program Title</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>program_title</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Program Title</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>program_title</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Program Title</t>
+          <t>End Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date_started</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Activities</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_ended</t>
+          <t>outcomes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Outcomes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>program_area</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Program Area</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>program_title</t>
+          <t>supporting_evidence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Program Title</t>
+          <t>Supporting Evidence</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date_ended</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Activities</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>List activities and projects that support your program's goals.</t>
-        </is>
-      </c>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -749,24 +745,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>outcomes</t>
+          <t>program_area_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Outcomes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Describe program outcomes or impacts (e.g., environmental benefits).</t>
-        </is>
-      </c>
+          <t>Program Area 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -776,24 +768,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>challenges</t>
+          <t>supporting_evidence_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Challenges</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Describe any challenges or barriers you faced during your program.</t>
-        </is>
-      </c>
+          <t>Supporting Evidence 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -803,24 +791,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>supporting_evidence</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Supporting Evidence</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Attach photos, videos, or documents to help illustrate your program.</t>
-        </is>
-      </c>
+          <t>Phone 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -835,269 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>program_area</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Program Area</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>program_title</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Program Title</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>date_ended</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Activities</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>outcomes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Outcomes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>supporting_evidence</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Supporting Evidence</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>program_area</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Program Area</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>program_title</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Program Title</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1114,10 +845,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1193,58 +924,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>program_area_choices</t>
+          <t>supporting_evidence_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eco-system</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eco-System</t>
+          <t>Photo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>program_area_choices</t>
+          <t>supporting_evidence_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>community_engagement</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Community Engagement</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>program_area_choices</t>
+          <t>supporting_evidence_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>climate_action</t>
+          <t>document</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Climate Action</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>program_area_choices</t>
+          <t>program_area_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1261,7 +992,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>program_area_choices</t>
+          <t>program_area_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1278,7 +1009,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>program_area_choices</t>
+          <t>program_area_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1295,7 +1026,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>supporting_evidence_choices</t>
+          <t>supporting_evidence_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1312,7 +1043,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>supporting_evidence_choices</t>
+          <t>supporting_evidence_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1329,7 +1060,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>supporting_evidence_choices</t>
+          <t>supporting_evidence_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1340,159 +1071,6 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Document</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>program_area_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>eco-system</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Eco-System</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>program_area_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>community_engagement</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Community Engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>program_area_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>climate_action</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Climate Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>supporting_evidence_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>photo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Photo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>supporting_evidence_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>supporting_evidence_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Document</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>program_area_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>eco-system</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Eco-System</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>program_area_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>community_engagement</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Community Engagement</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>program_area_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>climate_action</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Climate Action</t>
         </is>
       </c>
     </row>
